--- a/artfynd/A 16054-2024 artfynd.xlsx
+++ b/artfynd/A 16054-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118852651</v>
+        <v>118852638</v>
       </c>
       <c r="B2" t="n">
-        <v>95141</v>
+        <v>97867</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2869</v>
+        <v>221952</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>785254</v>
+        <v>785006</v>
       </c>
       <c r="R2" t="n">
-        <v>7291643</v>
+        <v>7291834</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118852649</v>
+        <v>118852640</v>
       </c>
       <c r="B3" t="n">
-        <v>82263</v>
+        <v>79565</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>785217</v>
+        <v>785020</v>
       </c>
       <c r="R3" t="n">
-        <v>7291592</v>
+        <v>7291865</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118858917</v>
+        <v>118852645</v>
       </c>
       <c r="B4" t="n">
-        <v>95141</v>
+        <v>78484</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>785060</v>
+        <v>784988</v>
       </c>
       <c r="R4" t="n">
-        <v>7291770</v>
+        <v>7291848</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,22 +969,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118852631</v>
+        <v>118852639</v>
       </c>
       <c r="B5" t="n">
-        <v>57443</v>
+        <v>97867</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>221952</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>785135</v>
+        <v>785101</v>
       </c>
       <c r="R5" t="n">
-        <v>7291671</v>
+        <v>7291777</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118858907</v>
+        <v>118858910</v>
       </c>
       <c r="B6" t="n">
-        <v>90504</v>
+        <v>97846</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,38 +1095,50 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Altertjärn A, Nb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>785260</v>
+        <v>785104</v>
       </c>
       <c r="R6" t="n">
-        <v>7291629</v>
+        <v>7291753</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1161,12 +1173,18 @@
           <t>2024-08-01</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Väldigt omfångsrik lokal på ca 10 m2</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1185,10 +1203,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118858903</v>
+        <v>118852630</v>
       </c>
       <c r="B7" t="n">
-        <v>58133</v>
+        <v>57443</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1215,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>208249</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1243,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>785102</v>
+        <v>784997</v>
       </c>
       <c r="R7" t="n">
-        <v>7291777</v>
+        <v>7291852</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1275,22 +1293,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118858844</v>
+        <v>118858843</v>
       </c>
       <c r="B8" t="n">
-        <v>78566</v>
+        <v>93874</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,25 +1317,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>864</v>
+        <v>2387</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1345,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>785031</v>
+        <v>785180</v>
       </c>
       <c r="R8" t="n">
-        <v>7291813</v>
+        <v>7291633</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1371,7 +1389,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1390,10 +1407,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118852646</v>
+        <v>118859586</v>
       </c>
       <c r="B9" t="n">
-        <v>78484</v>
+        <v>91083</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1402,25 +1419,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1179</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perenniporia subacida</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Peck) Donk</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1430,10 +1447,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>785230</v>
+        <v>784987</v>
       </c>
       <c r="R9" t="n">
-        <v>7291588</v>
+        <v>7291835</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1492,10 +1509,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118852629</v>
+        <v>118852646</v>
       </c>
       <c r="B10" t="n">
-        <v>79073</v>
+        <v>78484</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1508,21 +1525,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1532,10 +1549,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>784979</v>
+        <v>785230</v>
       </c>
       <c r="R10" t="n">
-        <v>7291836</v>
+        <v>7291588</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1594,10 +1611,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118852636</v>
+        <v>118858911</v>
       </c>
       <c r="B11" t="n">
-        <v>79594</v>
+        <v>97846</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1606,25 +1623,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1634,10 +1651,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>785067</v>
+        <v>785027</v>
       </c>
       <c r="R11" t="n">
-        <v>7291837</v>
+        <v>7291876</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1684,22 +1701,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118858905</v>
+        <v>118852649</v>
       </c>
       <c r="B12" t="n">
-        <v>58133</v>
+        <v>82263</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1708,25 +1725,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>208249</v>
+        <v>1312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1736,10 +1753,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>785162</v>
+        <v>785217</v>
       </c>
       <c r="R12" t="n">
-        <v>7291714</v>
+        <v>7291592</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1786,22 +1803,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118852644</v>
+        <v>118852650</v>
       </c>
       <c r="B13" t="n">
-        <v>58133</v>
+        <v>82263</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1810,25 +1827,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>208249</v>
+        <v>1312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1838,10 +1855,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>785262</v>
+        <v>785211</v>
       </c>
       <c r="R13" t="n">
-        <v>7291634</v>
+        <v>7291592</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1882,7 +1899,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1901,10 +1917,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118852638</v>
+        <v>118852633</v>
       </c>
       <c r="B14" t="n">
-        <v>97867</v>
+        <v>79594</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1917,21 +1933,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221952</v>
+        <v>6462</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1941,10 +1957,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>785006</v>
+        <v>785012</v>
       </c>
       <c r="R14" t="n">
-        <v>7291834</v>
+        <v>7291841</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2003,10 +2019,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118852632</v>
+        <v>118852648</v>
       </c>
       <c r="B15" t="n">
-        <v>79594</v>
+        <v>78484</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2015,25 +2031,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2043,10 +2059,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>784984</v>
+        <v>785137</v>
       </c>
       <c r="R15" t="n">
-        <v>7291846</v>
+        <v>7291669</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2105,10 +2121,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118852627</v>
+        <v>118852629</v>
       </c>
       <c r="B16" t="n">
-        <v>79102</v>
+        <v>79073</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2121,21 +2137,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2207,10 +2223,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118858915</v>
+        <v>118858903</v>
       </c>
       <c r="B17" t="n">
-        <v>82263</v>
+        <v>58133</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2219,25 +2235,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1312</v>
+        <v>208249</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2247,10 +2263,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>785229</v>
+        <v>785102</v>
       </c>
       <c r="R17" t="n">
-        <v>7291659</v>
+        <v>7291777</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2309,10 +2325,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118858843</v>
+        <v>118858904</v>
       </c>
       <c r="B18" t="n">
-        <v>93874</v>
+        <v>58133</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2325,21 +2341,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2387</v>
+        <v>208249</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2349,10 +2365,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>785180</v>
+        <v>785104</v>
       </c>
       <c r="R18" t="n">
-        <v>7291633</v>
+        <v>7291752</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2399,22 +2415,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118852630</v>
+        <v>118858905</v>
       </c>
       <c r="B19" t="n">
-        <v>57443</v>
+        <v>58133</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2423,25 +2439,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>208249</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2451,10 +2467,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>784997</v>
+        <v>785162</v>
       </c>
       <c r="R19" t="n">
-        <v>7291852</v>
+        <v>7291714</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2501,22 +2517,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118858910</v>
+        <v>118852641</v>
       </c>
       <c r="B20" t="n">
-        <v>97846</v>
+        <v>57401</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2525,50 +2541,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>103031</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Altertjärn A, Nb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>785104</v>
+        <v>785174</v>
       </c>
       <c r="R20" t="n">
-        <v>7291753</v>
+        <v>7291643</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2603,40 +2607,34 @@
           <t>2024-08-01</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Väldigt omfångsrik lokal på ca 10 m2</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118852648</v>
+        <v>118858908</v>
       </c>
       <c r="B21" t="n">
-        <v>78484</v>
+        <v>57443</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2649,21 +2647,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2673,10 +2671,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>785137</v>
+        <v>785101</v>
       </c>
       <c r="R21" t="n">
-        <v>7291669</v>
+        <v>7291732</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2723,22 +2721,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118852640</v>
+        <v>118858917</v>
       </c>
       <c r="B22" t="n">
-        <v>79565</v>
+        <v>95141</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2747,25 +2745,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>2869</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2775,10 +2773,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>785020</v>
+        <v>785060</v>
       </c>
       <c r="R22" t="n">
-        <v>7291865</v>
+        <v>7291770</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2825,19 +2823,19 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118852633</v>
+        <v>118852635</v>
       </c>
       <c r="B23" t="n">
         <v>79594</v>
@@ -2877,10 +2875,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>785012</v>
+        <v>785014</v>
       </c>
       <c r="R23" t="n">
-        <v>7291841</v>
+        <v>7291861</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2939,10 +2937,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118852628</v>
+        <v>118858906</v>
       </c>
       <c r="B24" t="n">
-        <v>79102</v>
+        <v>90504</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2955,21 +2953,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2979,10 +2977,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>784985</v>
+        <v>785102</v>
       </c>
       <c r="R24" t="n">
-        <v>7291854</v>
+        <v>7291747</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3029,22 +3027,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118858902</v>
+        <v>118858916</v>
       </c>
       <c r="B25" t="n">
-        <v>58133</v>
+        <v>79600</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3057,21 +3055,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>208249</v>
+        <v>6463</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3081,10 +3079,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>785056</v>
+        <v>784968</v>
       </c>
       <c r="R25" t="n">
-        <v>7291771</v>
+        <v>7291872</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3143,7 +3141,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118858911</v>
+        <v>118852643</v>
       </c>
       <c r="B26" t="n">
         <v>97846</v>
@@ -3183,10 +3181,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>785027</v>
+        <v>785111</v>
       </c>
       <c r="R26" t="n">
-        <v>7291876</v>
+        <v>7291785</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3233,22 +3231,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118858904</v>
+        <v>118852631</v>
       </c>
       <c r="B27" t="n">
-        <v>58133</v>
+        <v>57443</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3257,25 +3255,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>208249</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3285,10 +3283,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>785104</v>
+        <v>785135</v>
       </c>
       <c r="R27" t="n">
-        <v>7291752</v>
+        <v>7291671</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3335,22 +3333,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118858908</v>
+        <v>118858912</v>
       </c>
       <c r="B28" t="n">
-        <v>57443</v>
+        <v>78484</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3363,21 +3361,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3387,10 +3385,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>785101</v>
+        <v>785213</v>
       </c>
       <c r="R28" t="n">
-        <v>7291732</v>
+        <v>7291644</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3449,10 +3447,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118858909</v>
+        <v>118858907</v>
       </c>
       <c r="B29" t="n">
-        <v>91294</v>
+        <v>90504</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3465,21 +3463,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2014</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Koralltaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hericium coralloides</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Scop.) Pers.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3489,10 +3487,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>785056</v>
+        <v>785260</v>
       </c>
       <c r="R29" t="n">
-        <v>7291770</v>
+        <v>7291629</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3551,10 +3549,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118852642</v>
+        <v>118858844</v>
       </c>
       <c r="B30" t="n">
-        <v>97846</v>
+        <v>78566</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3563,25 +3561,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>864</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3591,10 +3589,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>785112</v>
+        <v>785031</v>
       </c>
       <c r="R30" t="n">
-        <v>7291778</v>
+        <v>7291813</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3635,6 +3633,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3653,10 +3652,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118852645</v>
+        <v>118852627</v>
       </c>
       <c r="B31" t="n">
-        <v>78484</v>
+        <v>79102</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3669,21 +3668,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3693,10 +3692,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>784988</v>
+        <v>784979</v>
       </c>
       <c r="R31" t="n">
-        <v>7291848</v>
+        <v>7291836</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3755,10 +3754,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118852643</v>
+        <v>118858914</v>
       </c>
       <c r="B32" t="n">
-        <v>97846</v>
+        <v>82263</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3767,25 +3766,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3795,10 +3794,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>785111</v>
+        <v>785157</v>
       </c>
       <c r="R32" t="n">
-        <v>7291785</v>
+        <v>7291723</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3845,22 +3844,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118858914</v>
+        <v>118852636</v>
       </c>
       <c r="B33" t="n">
-        <v>82263</v>
+        <v>79594</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3869,25 +3868,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1312</v>
+        <v>6462</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3897,10 +3896,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>785157</v>
+        <v>785067</v>
       </c>
       <c r="R33" t="n">
-        <v>7291723</v>
+        <v>7291837</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3947,22 +3946,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118858906</v>
+        <v>118858915</v>
       </c>
       <c r="B34" t="n">
-        <v>90504</v>
+        <v>82263</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3975,21 +3974,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3999,10 +3998,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>785102</v>
+        <v>785229</v>
       </c>
       <c r="R34" t="n">
-        <v>7291747</v>
+        <v>7291659</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4061,10 +4060,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118852641</v>
+        <v>118852644</v>
       </c>
       <c r="B35" t="n">
-        <v>57401</v>
+        <v>58133</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4077,21 +4076,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103031</v>
+        <v>208249</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4101,10 +4100,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>785174</v>
+        <v>785262</v>
       </c>
       <c r="R35" t="n">
-        <v>7291643</v>
+        <v>7291634</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4145,6 +4144,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4163,10 +4163,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118859586</v>
+        <v>118852651</v>
       </c>
       <c r="B36" t="n">
-        <v>91083</v>
+        <v>95141</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4175,25 +4175,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1179</v>
+        <v>2869</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gräddticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Perenniporia subacida</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Peck) Donk</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4203,10 +4203,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>784987</v>
+        <v>785254</v>
       </c>
       <c r="R36" t="n">
-        <v>7291835</v>
+        <v>7291643</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4265,10 +4265,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118858916</v>
+        <v>118852628</v>
       </c>
       <c r="B37" t="n">
-        <v>79600</v>
+        <v>79102</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4277,25 +4277,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6463</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4305,10 +4305,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>784968</v>
+        <v>784985</v>
       </c>
       <c r="R37" t="n">
-        <v>7291872</v>
+        <v>7291854</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4355,22 +4355,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>118852650</v>
+        <v>118852632</v>
       </c>
       <c r="B38" t="n">
-        <v>82263</v>
+        <v>79594</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4379,25 +4379,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1312</v>
+        <v>6462</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4407,10 +4407,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>785211</v>
+        <v>784984</v>
       </c>
       <c r="R38" t="n">
-        <v>7291592</v>
+        <v>7291846</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4469,10 +4469,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>118858912</v>
+        <v>118858902</v>
       </c>
       <c r="B39" t="n">
-        <v>78484</v>
+        <v>58133</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4481,25 +4481,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>208249</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4509,10 +4509,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>785213</v>
+        <v>785056</v>
       </c>
       <c r="R39" t="n">
-        <v>7291644</v>
+        <v>7291771</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4571,10 +4571,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>118852635</v>
+        <v>118852642</v>
       </c>
       <c r="B40" t="n">
-        <v>79594</v>
+        <v>97846</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4583,25 +4583,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>785014</v>
+        <v>785112</v>
       </c>
       <c r="R40" t="n">
-        <v>7291861</v>
+        <v>7291778</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4673,10 +4673,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>118852639</v>
+        <v>118858909</v>
       </c>
       <c r="B41" t="n">
-        <v>97867</v>
+        <v>91294</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4685,25 +4685,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>221952</v>
+        <v>2014</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Scop.) Pers.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4713,10 +4713,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>785101</v>
+        <v>785056</v>
       </c>
       <c r="R41" t="n">
-        <v>7291777</v>
+        <v>7291770</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4763,12 +4763,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>

--- a/artfynd/A 16054-2024 artfynd.xlsx
+++ b/artfynd/A 16054-2024 artfynd.xlsx
@@ -2529,10 +2529,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118852641</v>
+        <v>118858908</v>
       </c>
       <c r="B20" t="n">
-        <v>57401</v>
+        <v>57443</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2541,25 +2541,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103031</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2569,10 +2569,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>785174</v>
+        <v>785101</v>
       </c>
       <c r="R20" t="n">
-        <v>7291643</v>
+        <v>7291732</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2619,22 +2619,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118858908</v>
+        <v>118858917</v>
       </c>
       <c r="B21" t="n">
-        <v>57443</v>
+        <v>95141</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2643,25 +2643,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>2869</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>785101</v>
+        <v>785060</v>
       </c>
       <c r="R21" t="n">
-        <v>7291732</v>
+        <v>7291770</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2733,10 +2733,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118858917</v>
+        <v>118852641</v>
       </c>
       <c r="B22" t="n">
-        <v>95141</v>
+        <v>57401</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2749,21 +2749,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2869</v>
+        <v>103031</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2773,10 +2773,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>785060</v>
+        <v>785174</v>
       </c>
       <c r="R22" t="n">
-        <v>7291770</v>
+        <v>7291643</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2823,12 +2823,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>

--- a/artfynd/A 16054-2024 artfynd.xlsx
+++ b/artfynd/A 16054-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118852638</v>
+        <v>118852650</v>
       </c>
       <c r="B2" t="n">
-        <v>97867</v>
+        <v>82263</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221952</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>785006</v>
+        <v>785211</v>
       </c>
       <c r="R2" t="n">
-        <v>7291834</v>
+        <v>7291592</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118852640</v>
+        <v>118852635</v>
       </c>
       <c r="B3" t="n">
-        <v>79565</v>
+        <v>79594</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>785020</v>
+        <v>785014</v>
       </c>
       <c r="R3" t="n">
-        <v>7291865</v>
+        <v>7291861</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118852645</v>
+        <v>118852636</v>
       </c>
       <c r="B4" t="n">
-        <v>78484</v>
+        <v>79594</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>784988</v>
+        <v>785067</v>
       </c>
       <c r="R4" t="n">
-        <v>7291848</v>
+        <v>7291837</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118852639</v>
+        <v>118852649</v>
       </c>
       <c r="B5" t="n">
-        <v>97867</v>
+        <v>82263</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221952</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>785101</v>
+        <v>785217</v>
       </c>
       <c r="R5" t="n">
-        <v>7291777</v>
+        <v>7291592</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118858910</v>
+        <v>118852641</v>
       </c>
       <c r="B6" t="n">
-        <v>97846</v>
+        <v>57401</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,50 +1095,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>103031</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Altertjärn A, Nb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>785104</v>
+        <v>785174</v>
       </c>
       <c r="R6" t="n">
-        <v>7291753</v>
+        <v>7291643</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,40 +1161,34 @@
           <t>2024-08-01</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Väldigt omfångsrik lokal på ca 10 m2</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118852630</v>
+        <v>118858906</v>
       </c>
       <c r="B7" t="n">
-        <v>57443</v>
+        <v>90504</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1219,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1243,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>784997</v>
+        <v>785102</v>
       </c>
       <c r="R7" t="n">
-        <v>7291852</v>
+        <v>7291747</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1293,22 +1275,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118858843</v>
+        <v>118858911</v>
       </c>
       <c r="B8" t="n">
-        <v>93874</v>
+        <v>97846</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1317,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2387</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1345,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>785180</v>
+        <v>785027</v>
       </c>
       <c r="R8" t="n">
-        <v>7291633</v>
+        <v>7291876</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1395,22 +1377,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118859586</v>
+        <v>118852644</v>
       </c>
       <c r="B9" t="n">
-        <v>91083</v>
+        <v>58133</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1419,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1179</v>
+        <v>208249</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gräddticka</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Perenniporia subacida</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Peck) Donk</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1447,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>784987</v>
+        <v>785262</v>
       </c>
       <c r="R9" t="n">
-        <v>7291835</v>
+        <v>7291634</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,6 +1473,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1509,10 +1492,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118852646</v>
+        <v>118858844</v>
       </c>
       <c r="B10" t="n">
-        <v>78484</v>
+        <v>78566</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1525,21 +1508,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1549,10 +1532,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>785230</v>
+        <v>785031</v>
       </c>
       <c r="R10" t="n">
-        <v>7291588</v>
+        <v>7291813</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,6 +1576,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1611,10 +1595,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118858911</v>
+        <v>118852648</v>
       </c>
       <c r="B11" t="n">
-        <v>97846</v>
+        <v>78484</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1623,25 +1607,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1651,10 +1635,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>785027</v>
+        <v>785137</v>
       </c>
       <c r="R11" t="n">
-        <v>7291876</v>
+        <v>7291669</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1701,22 +1685,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118852649</v>
+        <v>118858903</v>
       </c>
       <c r="B12" t="n">
-        <v>82263</v>
+        <v>58133</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1725,25 +1709,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1312</v>
+        <v>208249</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1753,10 +1737,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>785217</v>
+        <v>785102</v>
       </c>
       <c r="R12" t="n">
-        <v>7291592</v>
+        <v>7291777</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1803,22 +1787,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118852650</v>
+        <v>118852646</v>
       </c>
       <c r="B13" t="n">
-        <v>82263</v>
+        <v>78484</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1831,21 +1815,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1855,10 +1839,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>785211</v>
+        <v>785230</v>
       </c>
       <c r="R13" t="n">
-        <v>7291592</v>
+        <v>7291588</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1917,10 +1901,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118852633</v>
+        <v>118859586</v>
       </c>
       <c r="B14" t="n">
-        <v>79594</v>
+        <v>91083</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1929,25 +1913,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6462</v>
+        <v>1179</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gräddticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Perenniporia subacida</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Peck) Donk</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1957,10 +1941,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>785012</v>
+        <v>784987</v>
       </c>
       <c r="R14" t="n">
-        <v>7291841</v>
+        <v>7291835</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2019,10 +2003,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118852648</v>
+        <v>118858907</v>
       </c>
       <c r="B15" t="n">
-        <v>78484</v>
+        <v>90504</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2035,21 +2019,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2059,10 +2043,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>785137</v>
+        <v>785260</v>
       </c>
       <c r="R15" t="n">
-        <v>7291669</v>
+        <v>7291629</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2109,22 +2093,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118852629</v>
+        <v>118858917</v>
       </c>
       <c r="B16" t="n">
-        <v>79073</v>
+        <v>95141</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2133,25 +2117,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>229821</v>
+        <v>2869</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2161,10 +2145,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>784979</v>
+        <v>785060</v>
       </c>
       <c r="R16" t="n">
-        <v>7291836</v>
+        <v>7291770</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2211,22 +2195,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118858903</v>
+        <v>118858908</v>
       </c>
       <c r="B17" t="n">
-        <v>58133</v>
+        <v>57443</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2235,25 +2219,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>208249</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2263,10 +2247,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>785102</v>
+        <v>785101</v>
       </c>
       <c r="R17" t="n">
-        <v>7291777</v>
+        <v>7291732</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2325,10 +2309,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118858904</v>
+        <v>118852643</v>
       </c>
       <c r="B18" t="n">
-        <v>58133</v>
+        <v>97846</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2337,25 +2321,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>208249</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2365,10 +2349,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>785104</v>
+        <v>785111</v>
       </c>
       <c r="R18" t="n">
-        <v>7291752</v>
+        <v>7291785</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2415,22 +2399,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118858905</v>
+        <v>118852651</v>
       </c>
       <c r="B19" t="n">
-        <v>58133</v>
+        <v>95141</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2443,21 +2427,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>208249</v>
+        <v>2869</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2467,10 +2451,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>785162</v>
+        <v>785254</v>
       </c>
       <c r="R19" t="n">
-        <v>7291714</v>
+        <v>7291643</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2517,22 +2501,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118858908</v>
+        <v>118852640</v>
       </c>
       <c r="B20" t="n">
-        <v>57443</v>
+        <v>79565</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2545,21 +2529,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2569,10 +2553,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>785101</v>
+        <v>785020</v>
       </c>
       <c r="R20" t="n">
-        <v>7291732</v>
+        <v>7291865</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2619,22 +2603,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118858917</v>
+        <v>118858915</v>
       </c>
       <c r="B21" t="n">
-        <v>95141</v>
+        <v>82263</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2643,25 +2627,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2869</v>
+        <v>1312</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2671,10 +2655,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>785060</v>
+        <v>785229</v>
       </c>
       <c r="R21" t="n">
-        <v>7291770</v>
+        <v>7291659</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2733,10 +2717,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118852641</v>
+        <v>118852633</v>
       </c>
       <c r="B22" t="n">
-        <v>57401</v>
+        <v>79594</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2749,21 +2733,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103031</v>
+        <v>6462</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2773,10 +2757,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>785174</v>
+        <v>785012</v>
       </c>
       <c r="R22" t="n">
-        <v>7291643</v>
+        <v>7291841</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2835,10 +2819,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118852635</v>
+        <v>118852629</v>
       </c>
       <c r="B23" t="n">
-        <v>79594</v>
+        <v>79073</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2847,25 +2831,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6462</v>
+        <v>229821</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2875,10 +2859,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>785014</v>
+        <v>784979</v>
       </c>
       <c r="R23" t="n">
-        <v>7291861</v>
+        <v>7291836</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2937,10 +2921,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118858906</v>
+        <v>118852627</v>
       </c>
       <c r="B24" t="n">
-        <v>90504</v>
+        <v>79102</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2953,21 +2937,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2977,10 +2961,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>785102</v>
+        <v>784979</v>
       </c>
       <c r="R24" t="n">
-        <v>7291747</v>
+        <v>7291836</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3027,22 +3011,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118858916</v>
+        <v>118852630</v>
       </c>
       <c r="B25" t="n">
-        <v>79600</v>
+        <v>57443</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3051,25 +3035,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6463</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3079,10 +3063,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>784968</v>
+        <v>784997</v>
       </c>
       <c r="R25" t="n">
-        <v>7291872</v>
+        <v>7291852</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3129,22 +3113,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118852643</v>
+        <v>118852645</v>
       </c>
       <c r="B26" t="n">
-        <v>97846</v>
+        <v>78484</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3153,25 +3137,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3181,10 +3165,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>785111</v>
+        <v>784988</v>
       </c>
       <c r="R26" t="n">
-        <v>7291785</v>
+        <v>7291848</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3243,10 +3227,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118852631</v>
+        <v>118858910</v>
       </c>
       <c r="B27" t="n">
-        <v>57443</v>
+        <v>97846</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3255,38 +3239,50 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Altertjärn A, Nb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>785135</v>
+        <v>785104</v>
       </c>
       <c r="R27" t="n">
-        <v>7291671</v>
+        <v>7291753</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3321,34 +3317,40 @@
           <t>2024-08-01</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Väldigt omfångsrik lokal på ca 10 m2</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118858912</v>
+        <v>118858843</v>
       </c>
       <c r="B28" t="n">
-        <v>78484</v>
+        <v>93874</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3357,25 +3359,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>2387</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3385,10 +3387,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>785213</v>
+        <v>785180</v>
       </c>
       <c r="R28" t="n">
-        <v>7291644</v>
+        <v>7291633</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3435,22 +3437,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118858907</v>
+        <v>118852632</v>
       </c>
       <c r="B29" t="n">
-        <v>90504</v>
+        <v>79594</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3459,25 +3461,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3487,10 +3489,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>785260</v>
+        <v>784984</v>
       </c>
       <c r="R29" t="n">
-        <v>7291629</v>
+        <v>7291846</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3537,22 +3539,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118858844</v>
+        <v>118858912</v>
       </c>
       <c r="B30" t="n">
-        <v>78566</v>
+        <v>78484</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3565,21 +3567,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3589,10 +3591,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>785031</v>
+        <v>785213</v>
       </c>
       <c r="R30" t="n">
-        <v>7291813</v>
+        <v>7291644</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3633,29 +3635,28 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118852627</v>
+        <v>118858904</v>
       </c>
       <c r="B31" t="n">
-        <v>79102</v>
+        <v>58133</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3664,25 +3665,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>208249</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3692,10 +3693,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>784979</v>
+        <v>785104</v>
       </c>
       <c r="R31" t="n">
-        <v>7291836</v>
+        <v>7291752</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3742,22 +3743,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118858914</v>
+        <v>118858909</v>
       </c>
       <c r="B32" t="n">
-        <v>82263</v>
+        <v>91294</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3770,21 +3771,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1312</v>
+        <v>2014</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Scop.) Pers.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3794,10 +3795,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>785157</v>
+        <v>785056</v>
       </c>
       <c r="R32" t="n">
-        <v>7291723</v>
+        <v>7291770</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3856,10 +3857,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118852636</v>
+        <v>118852628</v>
       </c>
       <c r="B33" t="n">
-        <v>79594</v>
+        <v>79102</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3868,25 +3869,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6462</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3896,10 +3897,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>785067</v>
+        <v>784985</v>
       </c>
       <c r="R33" t="n">
-        <v>7291837</v>
+        <v>7291854</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3958,10 +3959,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118858915</v>
+        <v>118858916</v>
       </c>
       <c r="B34" t="n">
-        <v>82263</v>
+        <v>79600</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3970,25 +3971,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1312</v>
+        <v>6463</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3998,10 +3999,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>785229</v>
+        <v>784968</v>
       </c>
       <c r="R34" t="n">
-        <v>7291659</v>
+        <v>7291872</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4060,10 +4061,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118852644</v>
+        <v>118852631</v>
       </c>
       <c r="B35" t="n">
-        <v>58133</v>
+        <v>57443</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4072,25 +4073,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>208249</v>
+        <v>103021</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4100,10 +4101,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>785262</v>
+        <v>785135</v>
       </c>
       <c r="R35" t="n">
-        <v>7291634</v>
+        <v>7291671</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4144,7 +4145,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4163,10 +4163,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118852651</v>
+        <v>118852638</v>
       </c>
       <c r="B36" t="n">
-        <v>95141</v>
+        <v>97867</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4179,21 +4179,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2869</v>
+        <v>221952</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4203,10 +4203,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>785254</v>
+        <v>785006</v>
       </c>
       <c r="R36" t="n">
-        <v>7291643</v>
+        <v>7291834</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4265,10 +4265,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118852628</v>
+        <v>118852639</v>
       </c>
       <c r="B37" t="n">
-        <v>79102</v>
+        <v>97867</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4277,25 +4277,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>221952</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4305,10 +4305,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>784985</v>
+        <v>785101</v>
       </c>
       <c r="R37" t="n">
-        <v>7291854</v>
+        <v>7291777</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4367,10 +4367,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>118852632</v>
+        <v>118852642</v>
       </c>
       <c r="B38" t="n">
-        <v>79594</v>
+        <v>97846</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4379,25 +4379,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4407,10 +4407,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>784984</v>
+        <v>785112</v>
       </c>
       <c r="R38" t="n">
-        <v>7291846</v>
+        <v>7291778</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4571,10 +4571,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>118852642</v>
+        <v>118858905</v>
       </c>
       <c r="B40" t="n">
-        <v>97846</v>
+        <v>58133</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4583,25 +4583,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>208249</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>785112</v>
+        <v>785162</v>
       </c>
       <c r="R40" t="n">
-        <v>7291778</v>
+        <v>7291714</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4661,22 +4661,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>118858909</v>
+        <v>118858914</v>
       </c>
       <c r="B41" t="n">
-        <v>91294</v>
+        <v>82263</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4689,21 +4689,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2014</v>
+        <v>1312</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Koralltaggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hericium coralloides</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Scop.) Pers.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4713,10 +4713,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>785056</v>
+        <v>785157</v>
       </c>
       <c r="R41" t="n">
-        <v>7291770</v>
+        <v>7291723</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>

--- a/artfynd/A 16054-2024 artfynd.xlsx
+++ b/artfynd/A 16054-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118852650</v>
+        <v>118858903</v>
       </c>
       <c r="B2" t="n">
-        <v>82263</v>
+        <v>58133</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>208249</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>785211</v>
+        <v>785102</v>
       </c>
       <c r="R2" t="n">
-        <v>7291592</v>
+        <v>7291777</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -765,22 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118852635</v>
+        <v>118852639</v>
       </c>
       <c r="B3" t="n">
-        <v>79594</v>
+        <v>97874</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>221952</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>785014</v>
+        <v>785101</v>
       </c>
       <c r="R3" t="n">
-        <v>7291861</v>
+        <v>7291777</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118852636</v>
+        <v>118852635</v>
       </c>
       <c r="B4" t="n">
-        <v>79594</v>
+        <v>79601</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>785067</v>
+        <v>785014</v>
       </c>
       <c r="R4" t="n">
-        <v>7291837</v>
+        <v>7291861</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118852649</v>
+        <v>118852644</v>
       </c>
       <c r="B5" t="n">
-        <v>82263</v>
+        <v>58133</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>208249</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>785217</v>
+        <v>785262</v>
       </c>
       <c r="R5" t="n">
-        <v>7291592</v>
+        <v>7291634</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1065,6 +1065,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1083,10 +1084,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118852641</v>
+        <v>118858906</v>
       </c>
       <c r="B6" t="n">
-        <v>57401</v>
+        <v>90511</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1096,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103031</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1124,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>785174</v>
+        <v>785102</v>
       </c>
       <c r="R6" t="n">
-        <v>7291643</v>
+        <v>7291747</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,22 +1174,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118858906</v>
+        <v>118852642</v>
       </c>
       <c r="B7" t="n">
-        <v>90504</v>
+        <v>97853</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1198,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1226,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>785102</v>
+        <v>785112</v>
       </c>
       <c r="R7" t="n">
-        <v>7291747</v>
+        <v>7291778</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1275,22 +1276,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118858911</v>
+        <v>118852628</v>
       </c>
       <c r="B8" t="n">
-        <v>97846</v>
+        <v>79109</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,25 +1300,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1328,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>785027</v>
+        <v>784985</v>
       </c>
       <c r="R8" t="n">
-        <v>7291876</v>
+        <v>7291854</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1377,22 +1378,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118852644</v>
+        <v>118852632</v>
       </c>
       <c r="B9" t="n">
-        <v>58133</v>
+        <v>79601</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1406,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>208249</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1430,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>785262</v>
+        <v>784984</v>
       </c>
       <c r="R9" t="n">
-        <v>7291634</v>
+        <v>7291846</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1473,7 +1474,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1492,10 +1492,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118858844</v>
+        <v>118858908</v>
       </c>
       <c r="B10" t="n">
-        <v>78566</v>
+        <v>57443</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1508,21 +1508,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>864</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1532,10 +1532,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>785031</v>
+        <v>785101</v>
       </c>
       <c r="R10" t="n">
-        <v>7291813</v>
+        <v>7291732</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1576,29 +1576,28 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118852648</v>
+        <v>118852629</v>
       </c>
       <c r="B11" t="n">
-        <v>78484</v>
+        <v>79080</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1611,21 +1610,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1635,10 +1634,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>785137</v>
+        <v>784979</v>
       </c>
       <c r="R11" t="n">
-        <v>7291669</v>
+        <v>7291836</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1697,10 +1696,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118858903</v>
+        <v>118859586</v>
       </c>
       <c r="B12" t="n">
-        <v>58133</v>
+        <v>91090</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1709,25 +1708,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>208249</v>
+        <v>1179</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Gräddticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Perenniporia subacida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Peck) Donk</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1737,10 +1736,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>785102</v>
+        <v>784987</v>
       </c>
       <c r="R12" t="n">
-        <v>7291777</v>
+        <v>7291835</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1787,22 +1786,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118852646</v>
+        <v>118852649</v>
       </c>
       <c r="B13" t="n">
-        <v>78484</v>
+        <v>82270</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1815,21 +1814,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1839,10 +1838,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>785230</v>
+        <v>785217</v>
       </c>
       <c r="R13" t="n">
-        <v>7291588</v>
+        <v>7291592</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1901,10 +1900,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118859586</v>
+        <v>118852643</v>
       </c>
       <c r="B14" t="n">
-        <v>91083</v>
+        <v>97853</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1917,21 +1916,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1179</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gräddticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Perenniporia subacida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Peck) Donk</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1941,10 +1940,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>784987</v>
+        <v>785111</v>
       </c>
       <c r="R14" t="n">
-        <v>7291835</v>
+        <v>7291785</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2003,10 +2002,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118858907</v>
+        <v>118858843</v>
       </c>
       <c r="B15" t="n">
-        <v>90504</v>
+        <v>93881</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2015,25 +2014,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>2387</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2043,10 +2042,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>785260</v>
+        <v>785180</v>
       </c>
       <c r="R15" t="n">
-        <v>7291629</v>
+        <v>7291633</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2093,22 +2092,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118858917</v>
+        <v>118858914</v>
       </c>
       <c r="B16" t="n">
-        <v>95141</v>
+        <v>82270</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2117,25 +2116,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2869</v>
+        <v>1312</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2145,10 +2144,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>785060</v>
+        <v>785157</v>
       </c>
       <c r="R16" t="n">
-        <v>7291770</v>
+        <v>7291723</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2207,10 +2206,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118858908</v>
+        <v>118858904</v>
       </c>
       <c r="B17" t="n">
-        <v>57443</v>
+        <v>58133</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2219,25 +2218,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>208249</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2247,10 +2246,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>785101</v>
+        <v>785104</v>
       </c>
       <c r="R17" t="n">
-        <v>7291732</v>
+        <v>7291752</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2309,10 +2308,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118852643</v>
+        <v>118852638</v>
       </c>
       <c r="B18" t="n">
-        <v>97846</v>
+        <v>97874</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2321,25 +2320,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2349,10 +2348,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>785111</v>
+        <v>785006</v>
       </c>
       <c r="R18" t="n">
-        <v>7291785</v>
+        <v>7291834</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2414,7 +2413,7 @@
         <v>118852651</v>
       </c>
       <c r="B19" t="n">
-        <v>95141</v>
+        <v>95148</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2513,10 +2512,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118852640</v>
+        <v>118852636</v>
       </c>
       <c r="B20" t="n">
-        <v>79565</v>
+        <v>79601</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2525,25 +2524,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2553,10 +2552,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>785020</v>
+        <v>785067</v>
       </c>
       <c r="R20" t="n">
-        <v>7291865</v>
+        <v>7291837</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2615,10 +2614,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118858915</v>
+        <v>118858902</v>
       </c>
       <c r="B21" t="n">
-        <v>82263</v>
+        <v>58133</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2627,25 +2626,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1312</v>
+        <v>208249</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2655,10 +2654,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>785229</v>
+        <v>785056</v>
       </c>
       <c r="R21" t="n">
-        <v>7291659</v>
+        <v>7291771</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2717,10 +2716,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118852633</v>
+        <v>118858917</v>
       </c>
       <c r="B22" t="n">
-        <v>79594</v>
+        <v>95148</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2733,21 +2732,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6462</v>
+        <v>2869</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2757,10 +2756,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>785012</v>
+        <v>785060</v>
       </c>
       <c r="R22" t="n">
-        <v>7291841</v>
+        <v>7291770</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2807,22 +2806,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118852629</v>
+        <v>118858844</v>
       </c>
       <c r="B23" t="n">
-        <v>79073</v>
+        <v>78573</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2835,21 +2834,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>229821</v>
+        <v>864</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2859,10 +2858,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>784979</v>
+        <v>785031</v>
       </c>
       <c r="R23" t="n">
-        <v>7291836</v>
+        <v>7291813</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2903,6 +2902,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2921,10 +2921,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118852627</v>
+        <v>118852645</v>
       </c>
       <c r="B24" t="n">
-        <v>79102</v>
+        <v>78491</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2937,21 +2937,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2961,10 +2961,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>784979</v>
+        <v>784988</v>
       </c>
       <c r="R24" t="n">
-        <v>7291836</v>
+        <v>7291848</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3023,10 +3023,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118852630</v>
+        <v>118852648</v>
       </c>
       <c r="B25" t="n">
-        <v>57443</v>
+        <v>78491</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3039,21 +3039,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3063,10 +3063,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>784997</v>
+        <v>785137</v>
       </c>
       <c r="R25" t="n">
-        <v>7291852</v>
+        <v>7291669</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3125,10 +3125,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118852645</v>
+        <v>118852627</v>
       </c>
       <c r="B26" t="n">
-        <v>78484</v>
+        <v>79109</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3141,21 +3141,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3165,10 +3165,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>784988</v>
+        <v>784979</v>
       </c>
       <c r="R26" t="n">
-        <v>7291848</v>
+        <v>7291836</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3227,10 +3227,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118858910</v>
+        <v>118852646</v>
       </c>
       <c r="B27" t="n">
-        <v>97846</v>
+        <v>78491</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3239,50 +3239,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Altertjärn A, Nb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>785104</v>
+        <v>785230</v>
       </c>
       <c r="R27" t="n">
-        <v>7291753</v>
+        <v>7291588</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3317,40 +3305,34 @@
           <t>2024-08-01</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Väldigt omfångsrik lokal på ca 10 m2</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118858843</v>
+        <v>118858912</v>
       </c>
       <c r="B28" t="n">
-        <v>93874</v>
+        <v>78491</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3359,25 +3341,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2387</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3387,10 +3369,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>785180</v>
+        <v>785213</v>
       </c>
       <c r="R28" t="n">
-        <v>7291633</v>
+        <v>7291644</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3437,22 +3419,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118852632</v>
+        <v>118852650</v>
       </c>
       <c r="B29" t="n">
-        <v>79594</v>
+        <v>82270</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3461,25 +3443,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6462</v>
+        <v>1312</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3489,10 +3471,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>784984</v>
+        <v>785211</v>
       </c>
       <c r="R29" t="n">
-        <v>7291846</v>
+        <v>7291592</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3551,10 +3533,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118858912</v>
+        <v>118858915</v>
       </c>
       <c r="B30" t="n">
-        <v>78484</v>
+        <v>82270</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3567,21 +3549,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3591,10 +3573,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>785213</v>
+        <v>785229</v>
       </c>
       <c r="R30" t="n">
-        <v>7291644</v>
+        <v>7291659</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3653,10 +3635,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118858904</v>
+        <v>118858909</v>
       </c>
       <c r="B31" t="n">
-        <v>58133</v>
+        <v>91301</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3665,25 +3647,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>208249</v>
+        <v>2014</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Scop.) Pers.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3693,10 +3675,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>785104</v>
+        <v>785056</v>
       </c>
       <c r="R31" t="n">
-        <v>7291752</v>
+        <v>7291770</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3755,10 +3737,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118858909</v>
+        <v>118858910</v>
       </c>
       <c r="B32" t="n">
-        <v>91294</v>
+        <v>97853</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3767,38 +3749,50 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2014</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Koralltaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hericium coralloides</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Scop.) Pers.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Altertjärn A, Nb</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>785056</v>
+        <v>785104</v>
       </c>
       <c r="R32" t="n">
-        <v>7291770</v>
+        <v>7291753</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3833,12 +3827,18 @@
           <t>2024-08-01</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Väldigt omfångsrik lokal på ca 10 m2</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3857,10 +3857,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118852628</v>
+        <v>118858907</v>
       </c>
       <c r="B33" t="n">
-        <v>79102</v>
+        <v>90511</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3873,21 +3873,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3897,10 +3897,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>784985</v>
+        <v>785260</v>
       </c>
       <c r="R33" t="n">
-        <v>7291854</v>
+        <v>7291629</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3947,22 +3947,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118858916</v>
+        <v>118852633</v>
       </c>
       <c r="B34" t="n">
-        <v>79600</v>
+        <v>79601</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3975,21 +3975,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3999,10 +3999,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>784968</v>
+        <v>785012</v>
       </c>
       <c r="R34" t="n">
-        <v>7291872</v>
+        <v>7291841</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4049,12 +4049,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4163,10 +4163,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118852638</v>
+        <v>118852640</v>
       </c>
       <c r="B36" t="n">
-        <v>97867</v>
+        <v>79572</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4175,25 +4175,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4203,10 +4203,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>785006</v>
+        <v>785020</v>
       </c>
       <c r="R36" t="n">
-        <v>7291834</v>
+        <v>7291865</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4265,10 +4265,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118852639</v>
+        <v>118852630</v>
       </c>
       <c r="B37" t="n">
-        <v>97867</v>
+        <v>57443</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4277,25 +4277,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221952</v>
+        <v>103021</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4305,10 +4305,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>785101</v>
+        <v>784997</v>
       </c>
       <c r="R37" t="n">
-        <v>7291777</v>
+        <v>7291852</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4367,10 +4367,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>118852642</v>
+        <v>118852641</v>
       </c>
       <c r="B38" t="n">
-        <v>97846</v>
+        <v>57401</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4379,25 +4379,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>103031</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4407,10 +4407,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>785112</v>
+        <v>785174</v>
       </c>
       <c r="R38" t="n">
-        <v>7291778</v>
+        <v>7291643</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4469,7 +4469,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>118858902</v>
+        <v>118858905</v>
       </c>
       <c r="B39" t="n">
         <v>58133</v>
@@ -4509,10 +4509,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>785056</v>
+        <v>785162</v>
       </c>
       <c r="R39" t="n">
-        <v>7291771</v>
+        <v>7291714</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4571,10 +4571,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>118858905</v>
+        <v>118858916</v>
       </c>
       <c r="B40" t="n">
-        <v>58133</v>
+        <v>79607</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4587,21 +4587,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>208249</v>
+        <v>6463</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>785162</v>
+        <v>784968</v>
       </c>
       <c r="R40" t="n">
-        <v>7291714</v>
+        <v>7291872</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4673,10 +4673,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>118858914</v>
+        <v>118858911</v>
       </c>
       <c r="B41" t="n">
-        <v>82263</v>
+        <v>97853</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4685,25 +4685,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4713,10 +4713,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>785157</v>
+        <v>785027</v>
       </c>
       <c r="R41" t="n">
-        <v>7291723</v>
+        <v>7291876</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>

--- a/artfynd/A 16054-2024 artfynd.xlsx
+++ b/artfynd/A 16054-2024 artfynd.xlsx
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118852644</v>
+        <v>118852642</v>
       </c>
       <c r="B5" t="n">
-        <v>58133</v>
+        <v>97853</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>208249</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>785262</v>
+        <v>785112</v>
       </c>
       <c r="R5" t="n">
-        <v>7291634</v>
+        <v>7291778</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1065,7 +1065,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1186,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118852642</v>
+        <v>118852644</v>
       </c>
       <c r="B7" t="n">
-        <v>97853</v>
+        <v>58133</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1198,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>208249</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1226,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>785112</v>
+        <v>785262</v>
       </c>
       <c r="R7" t="n">
-        <v>7291778</v>
+        <v>7291634</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1270,6 +1269,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1900,10 +1900,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118852643</v>
+        <v>118858904</v>
       </c>
       <c r="B14" t="n">
-        <v>97853</v>
+        <v>58133</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1912,25 +1912,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>208249</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1940,10 +1940,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>785111</v>
+        <v>785104</v>
       </c>
       <c r="R14" t="n">
-        <v>7291785</v>
+        <v>7291752</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1990,22 +1990,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118858843</v>
+        <v>118852643</v>
       </c>
       <c r="B15" t="n">
-        <v>93881</v>
+        <v>97853</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2014,25 +2014,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2387</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2042,10 +2042,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>785180</v>
+        <v>785111</v>
       </c>
       <c r="R15" t="n">
-        <v>7291633</v>
+        <v>7291785</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2206,10 +2206,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118858904</v>
+        <v>118858843</v>
       </c>
       <c r="B17" t="n">
-        <v>58133</v>
+        <v>93881</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2222,21 +2222,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>208249</v>
+        <v>2387</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2246,10 +2246,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>785104</v>
+        <v>785180</v>
       </c>
       <c r="R17" t="n">
-        <v>7291752</v>
+        <v>7291633</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2296,12 +2296,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2410,10 +2410,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118852651</v>
+        <v>118852636</v>
       </c>
       <c r="B19" t="n">
-        <v>95148</v>
+        <v>79601</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2426,21 +2426,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2869</v>
+        <v>6462</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2450,10 +2450,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>785254</v>
+        <v>785067</v>
       </c>
       <c r="R19" t="n">
-        <v>7291643</v>
+        <v>7291837</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2512,10 +2512,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118852636</v>
+        <v>118852651</v>
       </c>
       <c r="B20" t="n">
-        <v>79601</v>
+        <v>95148</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2528,21 +2528,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6462</v>
+        <v>2869</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2552,10 +2552,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>785067</v>
+        <v>785254</v>
       </c>
       <c r="R20" t="n">
-        <v>7291837</v>
+        <v>7291643</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3125,10 +3125,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118852627</v>
+        <v>118858912</v>
       </c>
       <c r="B26" t="n">
-        <v>79109</v>
+        <v>78491</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3141,21 +3141,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3165,10 +3165,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>784979</v>
+        <v>785213</v>
       </c>
       <c r="R26" t="n">
-        <v>7291836</v>
+        <v>7291644</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3215,22 +3215,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118852646</v>
+        <v>118852627</v>
       </c>
       <c r="B27" t="n">
-        <v>78491</v>
+        <v>79109</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3243,21 +3243,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3267,10 +3267,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>785230</v>
+        <v>784979</v>
       </c>
       <c r="R27" t="n">
-        <v>7291588</v>
+        <v>7291836</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3329,7 +3329,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118858912</v>
+        <v>118852646</v>
       </c>
       <c r="B28" t="n">
         <v>78491</v>
@@ -3369,10 +3369,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>785213</v>
+        <v>785230</v>
       </c>
       <c r="R28" t="n">
-        <v>7291644</v>
+        <v>7291588</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3419,12 +3419,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -3635,10 +3635,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118858909</v>
+        <v>118858910</v>
       </c>
       <c r="B31" t="n">
-        <v>91301</v>
+        <v>97853</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3647,38 +3647,50 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2014</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Koralltaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hericium coralloides</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Scop.) Pers.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Altertjärn A, Nb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>785056</v>
+        <v>785104</v>
       </c>
       <c r="R31" t="n">
-        <v>7291770</v>
+        <v>7291753</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3713,12 +3725,18 @@
           <t>2024-08-01</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Väldigt omfångsrik lokal på ca 10 m2</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3737,10 +3755,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118858910</v>
+        <v>118858907</v>
       </c>
       <c r="B32" t="n">
-        <v>97853</v>
+        <v>90511</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3749,50 +3767,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Altertjärn A, Nb</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>785104</v>
+        <v>785260</v>
       </c>
       <c r="R32" t="n">
-        <v>7291753</v>
+        <v>7291629</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3827,18 +3833,12 @@
           <t>2024-08-01</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Väldigt omfångsrik lokal på ca 10 m2</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3857,10 +3857,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118858907</v>
+        <v>118858909</v>
       </c>
       <c r="B33" t="n">
-        <v>90511</v>
+        <v>91301</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3873,21 +3873,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>2014</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) Pers.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3897,10 +3897,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>785260</v>
+        <v>785056</v>
       </c>
       <c r="R33" t="n">
-        <v>7291629</v>
+        <v>7291770</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3959,10 +3959,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118852633</v>
+        <v>118852631</v>
       </c>
       <c r="B34" t="n">
-        <v>79601</v>
+        <v>57443</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3971,25 +3971,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6462</v>
+        <v>103021</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3999,10 +3999,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>785012</v>
+        <v>785135</v>
       </c>
       <c r="R34" t="n">
-        <v>7291841</v>
+        <v>7291671</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4061,10 +4061,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118852631</v>
+        <v>118852633</v>
       </c>
       <c r="B35" t="n">
-        <v>57443</v>
+        <v>79601</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4073,25 +4073,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103021</v>
+        <v>6462</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4101,10 +4101,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>785135</v>
+        <v>785012</v>
       </c>
       <c r="R35" t="n">
-        <v>7291671</v>
+        <v>7291841</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4163,10 +4163,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118852640</v>
+        <v>118852641</v>
       </c>
       <c r="B36" t="n">
-        <v>79572</v>
+        <v>57401</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4175,25 +4175,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>103031</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4203,10 +4203,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>785020</v>
+        <v>785174</v>
       </c>
       <c r="R36" t="n">
-        <v>7291865</v>
+        <v>7291643</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4265,10 +4265,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118852630</v>
+        <v>118852640</v>
       </c>
       <c r="B37" t="n">
-        <v>57443</v>
+        <v>79572</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4281,21 +4281,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4305,10 +4305,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>784997</v>
+        <v>785020</v>
       </c>
       <c r="R37" t="n">
-        <v>7291852</v>
+        <v>7291865</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4367,10 +4367,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>118852641</v>
+        <v>118852630</v>
       </c>
       <c r="B38" t="n">
-        <v>57401</v>
+        <v>57443</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4379,25 +4379,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103031</v>
+        <v>103021</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4407,10 +4407,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>785174</v>
+        <v>784997</v>
       </c>
       <c r="R38" t="n">
-        <v>7291643</v>
+        <v>7291852</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>

--- a/artfynd/A 16054-2024 artfynd.xlsx
+++ b/artfynd/A 16054-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118858903</v>
+        <v>118858915</v>
       </c>
       <c r="B2" t="n">
-        <v>58133</v>
+        <v>82270</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>208249</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>785102</v>
+        <v>785229</v>
       </c>
       <c r="R2" t="n">
-        <v>7291777</v>
+        <v>7291659</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118852639</v>
+        <v>118852649</v>
       </c>
       <c r="B3" t="n">
-        <v>97874</v>
+        <v>82270</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221952</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>785101</v>
+        <v>785217</v>
       </c>
       <c r="R3" t="n">
-        <v>7291777</v>
+        <v>7291592</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118852635</v>
+        <v>118852632</v>
       </c>
       <c r="B4" t="n">
         <v>79601</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>785014</v>
+        <v>784984</v>
       </c>
       <c r="R4" t="n">
-        <v>7291861</v>
+        <v>7291846</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118852642</v>
+        <v>118852635</v>
       </c>
       <c r="B5" t="n">
-        <v>97853</v>
+        <v>79601</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>785112</v>
+        <v>785014</v>
       </c>
       <c r="R5" t="n">
-        <v>7291778</v>
+        <v>7291861</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118858906</v>
+        <v>118858912</v>
       </c>
       <c r="B6" t="n">
-        <v>90511</v>
+        <v>78491</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>785102</v>
+        <v>785213</v>
       </c>
       <c r="R6" t="n">
-        <v>7291747</v>
+        <v>7291644</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118852644</v>
+        <v>118858909</v>
       </c>
       <c r="B7" t="n">
-        <v>58133</v>
+        <v>91301</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>208249</v>
+        <v>2014</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Scop.) Pers.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>785262</v>
+        <v>785056</v>
       </c>
       <c r="R7" t="n">
-        <v>7291634</v>
+        <v>7291770</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1269,29 +1269,28 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118852628</v>
+        <v>118858917</v>
       </c>
       <c r="B8" t="n">
-        <v>79109</v>
+        <v>95148</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1300,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>2869</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1328,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>784985</v>
+        <v>785060</v>
       </c>
       <c r="R8" t="n">
-        <v>7291854</v>
+        <v>7291770</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1378,22 +1377,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118852632</v>
+        <v>118858904</v>
       </c>
       <c r="B9" t="n">
-        <v>79601</v>
+        <v>58133</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1406,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>208249</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1430,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>784984</v>
+        <v>785104</v>
       </c>
       <c r="R9" t="n">
-        <v>7291846</v>
+        <v>7291752</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1480,22 +1479,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118858908</v>
+        <v>118858843</v>
       </c>
       <c r="B10" t="n">
-        <v>57443</v>
+        <v>93881</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1504,25 +1503,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>2387</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1532,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>785101</v>
+        <v>785180</v>
       </c>
       <c r="R10" t="n">
-        <v>7291732</v>
+        <v>7291633</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1582,22 +1581,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118852629</v>
+        <v>118852636</v>
       </c>
       <c r="B11" t="n">
-        <v>79080</v>
+        <v>79601</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1606,25 +1605,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>229821</v>
+        <v>6462</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1634,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>784979</v>
+        <v>785067</v>
       </c>
       <c r="R11" t="n">
-        <v>7291836</v>
+        <v>7291837</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1696,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118859586</v>
+        <v>118858916</v>
       </c>
       <c r="B12" t="n">
-        <v>91090</v>
+        <v>79607</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1708,25 +1707,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1179</v>
+        <v>6463</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gräddticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Perenniporia subacida</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Peck) Donk</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1736,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>784987</v>
+        <v>784968</v>
       </c>
       <c r="R12" t="n">
-        <v>7291835</v>
+        <v>7291872</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1786,22 +1785,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118852649</v>
+        <v>118858910</v>
       </c>
       <c r="B13" t="n">
-        <v>82270</v>
+        <v>97853</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1810,38 +1809,50 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Altertjärn A, Nb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>785217</v>
+        <v>785104</v>
       </c>
       <c r="R13" t="n">
-        <v>7291592</v>
+        <v>7291753</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1876,31 +1887,37 @@
           <t>2024-08-01</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Väldigt omfångsrik lokal på ca 10 m2</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118858904</v>
+        <v>118858905</v>
       </c>
       <c r="B14" t="n">
         <v>58133</v>
@@ -1940,10 +1957,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>785104</v>
+        <v>785162</v>
       </c>
       <c r="R14" t="n">
-        <v>7291752</v>
+        <v>7291714</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2002,10 +2019,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118852643</v>
+        <v>118858907</v>
       </c>
       <c r="B15" t="n">
-        <v>97853</v>
+        <v>90511</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2014,25 +2031,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2042,10 +2059,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>785111</v>
+        <v>785260</v>
       </c>
       <c r="R15" t="n">
-        <v>7291785</v>
+        <v>7291629</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2092,22 +2109,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118858914</v>
+        <v>118852638</v>
       </c>
       <c r="B16" t="n">
-        <v>82270</v>
+        <v>97874</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2116,25 +2133,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1312</v>
+        <v>221952</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2144,10 +2161,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>785157</v>
+        <v>785006</v>
       </c>
       <c r="R16" t="n">
-        <v>7291723</v>
+        <v>7291834</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2194,22 +2211,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118858843</v>
+        <v>118858914</v>
       </c>
       <c r="B17" t="n">
-        <v>93881</v>
+        <v>82270</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2218,25 +2235,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2387</v>
+        <v>1312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2246,10 +2263,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>785180</v>
+        <v>785157</v>
       </c>
       <c r="R17" t="n">
-        <v>7291633</v>
+        <v>7291723</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2296,22 +2313,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118852638</v>
+        <v>118852631</v>
       </c>
       <c r="B18" t="n">
-        <v>97874</v>
+        <v>57443</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2320,25 +2337,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221952</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2348,10 +2365,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>785006</v>
+        <v>785135</v>
       </c>
       <c r="R18" t="n">
-        <v>7291834</v>
+        <v>7291671</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2410,10 +2427,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118852636</v>
+        <v>118852648</v>
       </c>
       <c r="B19" t="n">
-        <v>79601</v>
+        <v>78491</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2422,25 +2439,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2450,10 +2467,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>785067</v>
+        <v>785137</v>
       </c>
       <c r="R19" t="n">
-        <v>7291837</v>
+        <v>7291669</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2512,10 +2529,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118852651</v>
+        <v>118858911</v>
       </c>
       <c r="B20" t="n">
-        <v>95148</v>
+        <v>97853</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2524,25 +2541,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2552,10 +2569,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>785254</v>
+        <v>785027</v>
       </c>
       <c r="R20" t="n">
-        <v>7291643</v>
+        <v>7291876</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2602,22 +2619,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118858902</v>
+        <v>118852643</v>
       </c>
       <c r="B21" t="n">
-        <v>58133</v>
+        <v>97853</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2626,25 +2643,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>208249</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2654,10 +2671,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>785056</v>
+        <v>785111</v>
       </c>
       <c r="R21" t="n">
-        <v>7291771</v>
+        <v>7291785</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2704,22 +2721,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118858917</v>
+        <v>118858906</v>
       </c>
       <c r="B22" t="n">
-        <v>95148</v>
+        <v>90511</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2728,25 +2745,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2869</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2756,10 +2773,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>785060</v>
+        <v>785102</v>
       </c>
       <c r="R22" t="n">
-        <v>7291770</v>
+        <v>7291747</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2818,10 +2835,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118858844</v>
+        <v>118852645</v>
       </c>
       <c r="B23" t="n">
-        <v>78573</v>
+        <v>78491</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2834,21 +2851,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2858,10 +2875,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>785031</v>
+        <v>784988</v>
       </c>
       <c r="R23" t="n">
-        <v>7291813</v>
+        <v>7291848</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2902,7 +2919,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2921,10 +2937,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118852645</v>
+        <v>118852628</v>
       </c>
       <c r="B24" t="n">
-        <v>78491</v>
+        <v>79109</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2937,21 +2953,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2961,10 +2977,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>784988</v>
+        <v>784985</v>
       </c>
       <c r="R24" t="n">
-        <v>7291848</v>
+        <v>7291854</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3023,10 +3039,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118852648</v>
+        <v>118852650</v>
       </c>
       <c r="B25" t="n">
-        <v>78491</v>
+        <v>82270</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3039,21 +3055,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3063,10 +3079,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>785137</v>
+        <v>785211</v>
       </c>
       <c r="R25" t="n">
-        <v>7291669</v>
+        <v>7291592</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3125,10 +3141,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118858912</v>
+        <v>118859586</v>
       </c>
       <c r="B26" t="n">
-        <v>78491</v>
+        <v>91090</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3137,25 +3153,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>1179</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perenniporia subacida</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Peck) Donk</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3165,10 +3181,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>785213</v>
+        <v>784987</v>
       </c>
       <c r="R26" t="n">
-        <v>7291644</v>
+        <v>7291835</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3215,22 +3231,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118852627</v>
+        <v>118852630</v>
       </c>
       <c r="B27" t="n">
-        <v>79109</v>
+        <v>57443</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3243,21 +3259,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3267,10 +3283,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>784979</v>
+        <v>784997</v>
       </c>
       <c r="R27" t="n">
-        <v>7291836</v>
+        <v>7291852</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3329,10 +3345,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118852646</v>
+        <v>118858902</v>
       </c>
       <c r="B28" t="n">
-        <v>78491</v>
+        <v>58133</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3341,25 +3357,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>208249</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3369,10 +3385,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>785230</v>
+        <v>785056</v>
       </c>
       <c r="R28" t="n">
-        <v>7291588</v>
+        <v>7291771</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3419,22 +3435,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118852650</v>
+        <v>118852644</v>
       </c>
       <c r="B29" t="n">
-        <v>82270</v>
+        <v>58133</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3443,25 +3459,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1312</v>
+        <v>208249</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3471,10 +3487,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>785211</v>
+        <v>785262</v>
       </c>
       <c r="R29" t="n">
-        <v>7291592</v>
+        <v>7291634</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3515,6 +3531,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3533,10 +3550,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118858915</v>
+        <v>118852651</v>
       </c>
       <c r="B30" t="n">
-        <v>82270</v>
+        <v>95148</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3545,25 +3562,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1312</v>
+        <v>2869</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3573,10 +3590,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>785229</v>
+        <v>785254</v>
       </c>
       <c r="R30" t="n">
-        <v>7291659</v>
+        <v>7291643</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3623,22 +3640,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118858910</v>
+        <v>118852640</v>
       </c>
       <c r="B31" t="n">
-        <v>97853</v>
+        <v>79572</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3647,50 +3664,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Altertjärn A, Nb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>785104</v>
+        <v>785020</v>
       </c>
       <c r="R31" t="n">
-        <v>7291753</v>
+        <v>7291865</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3725,40 +3730,34 @@
           <t>2024-08-01</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Väldigt omfångsrik lokal på ca 10 m2</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118858907</v>
+        <v>118852646</v>
       </c>
       <c r="B32" t="n">
-        <v>90511</v>
+        <v>78491</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3771,21 +3770,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3795,10 +3794,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>785260</v>
+        <v>785230</v>
       </c>
       <c r="R32" t="n">
-        <v>7291629</v>
+        <v>7291588</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3845,22 +3844,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118858909</v>
+        <v>118852641</v>
       </c>
       <c r="B33" t="n">
-        <v>91301</v>
+        <v>57401</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3869,25 +3868,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2014</v>
+        <v>103031</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Koralltaggsvamp</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hericium coralloides</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scop.) Pers.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3897,10 +3896,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>785056</v>
+        <v>785174</v>
       </c>
       <c r="R33" t="n">
-        <v>7291770</v>
+        <v>7291643</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3947,22 +3946,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118852631</v>
+        <v>118852629</v>
       </c>
       <c r="B34" t="n">
-        <v>57443</v>
+        <v>79080</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3975,21 +3974,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103021</v>
+        <v>229821</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3999,10 +3998,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>785135</v>
+        <v>784979</v>
       </c>
       <c r="R34" t="n">
-        <v>7291671</v>
+        <v>7291836</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4061,10 +4060,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118852633</v>
+        <v>118858844</v>
       </c>
       <c r="B35" t="n">
-        <v>79601</v>
+        <v>78573</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4073,25 +4072,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6462</v>
+        <v>864</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4101,10 +4100,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>785012</v>
+        <v>785031</v>
       </c>
       <c r="R35" t="n">
-        <v>7291841</v>
+        <v>7291813</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4145,6 +4144,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4163,10 +4163,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118852641</v>
+        <v>118852642</v>
       </c>
       <c r="B36" t="n">
-        <v>57401</v>
+        <v>97853</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4175,25 +4175,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103031</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4203,10 +4203,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>785174</v>
+        <v>785112</v>
       </c>
       <c r="R36" t="n">
-        <v>7291643</v>
+        <v>7291778</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4265,10 +4265,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118852640</v>
+        <v>118852627</v>
       </c>
       <c r="B37" t="n">
-        <v>79572</v>
+        <v>79109</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4281,21 +4281,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4305,10 +4305,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>785020</v>
+        <v>784979</v>
       </c>
       <c r="R37" t="n">
-        <v>7291865</v>
+        <v>7291836</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4367,7 +4367,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>118852630</v>
+        <v>118858908</v>
       </c>
       <c r="B38" t="n">
         <v>57443</v>
@@ -4407,10 +4407,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>784997</v>
+        <v>785101</v>
       </c>
       <c r="R38" t="n">
-        <v>7291852</v>
+        <v>7291732</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4457,19 +4457,19 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>118858905</v>
+        <v>118858903</v>
       </c>
       <c r="B39" t="n">
         <v>58133</v>
@@ -4509,10 +4509,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>785162</v>
+        <v>785102</v>
       </c>
       <c r="R39" t="n">
-        <v>7291714</v>
+        <v>7291777</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4571,10 +4571,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>118858916</v>
+        <v>118852639</v>
       </c>
       <c r="B40" t="n">
-        <v>79607</v>
+        <v>97874</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4587,21 +4587,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6463</v>
+        <v>221952</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>784968</v>
+        <v>785101</v>
       </c>
       <c r="R40" t="n">
-        <v>7291872</v>
+        <v>7291777</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4661,22 +4661,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>118858911</v>
+        <v>118852633</v>
       </c>
       <c r="B41" t="n">
-        <v>97853</v>
+        <v>79601</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4685,25 +4685,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4713,10 +4713,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>785027</v>
+        <v>785012</v>
       </c>
       <c r="R41" t="n">
-        <v>7291876</v>
+        <v>7291841</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4763,12 +4763,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
